--- a/Config/Excel/language/lang_system.xlsx
+++ b/Config/Excel/language/lang_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="9880"/>
+    <workbookView windowWidth="29865" windowHeight="12735"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>id</t>
   </si>
   <si>
     <t>text</t>
+  </si>
+  <si>
+    <t>color</t>
   </si>
   <si>
     <t>c</t>
@@ -1026,75 +1029,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="1"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="19.6363636363636" customWidth="1"/>
-    <col min="2" max="2" width="37.2545454545455" customWidth="1"/>
+    <col min="1" max="1" width="19.6333333333333" customWidth="1"/>
+    <col min="2" max="2" width="37.2583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>910001</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>910002</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>910003</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>910004</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1108,7 +1135,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1120,7 +1147,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Excel/language/lang_system.xlsx
+++ b/Config/Excel/language/lang_system.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,24 @@
   </si>
   <si>
     <t>结束游戏</t>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>属性</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>职业</t>
+  </si>
+  <si>
+    <t>任务</t>
+  </si>
+  <si>
+    <t>其他</t>
   </si>
 </sst>
 </file>
@@ -1029,8 +1047,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="19.6333333333333" customWidth="1"/>
     <col min="2" max="2" width="37.2583333333333" customWidth="1"/>
@@ -1122,6 +1140,102 @@
       </c>
       <c r="C8">
         <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>910005</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>910006</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>910007</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>910008</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>910009</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>910010</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>910011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>910012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>910013</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>910014</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>910015</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>910016</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/language/lang_system.xlsx
+++ b/Config/Excel/language/lang_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29865" windowHeight="12735"/>
+    <workbookView windowWidth="27945" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -1047,7 +1047,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="19.6333333333333" customWidth="1"/>
@@ -1208,34 +1208,103 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>910011</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
+      <c r="B15"/>
+      <c r="C15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>910012</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16"/>
+      <c r="C16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>910013</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17"/>
+      <c r="C17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>910014</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18"/>
+      <c r="C18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>910015</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19"/>
+      <c r="C19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>910016</v>
+      </c>
+      <c r="B20"/>
+      <c r="C20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>910017</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>910018</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>910019</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>910020</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>910021</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>910022</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>910023</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>910024</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>910025</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/language/lang_system.xlsx
+++ b/Config/Excel/language/lang_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="29865" windowHeight="12735"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>id</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>其他</t>
+  </si>
+  <si>
+    <t>{0}/{1}</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1215,9 @@
       <c r="A15">
         <v>910011</v>
       </c>
-      <c r="B15"/>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
       <c r="C15">
         <v>3</v>
       </c>

--- a/Config/Excel/language/lang_system.xlsx
+++ b/Config/Excel/language/lang_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29865" windowHeight="12735"/>
+    <workbookView windowWidth="27945" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -83,6 +83,21 @@
   </si>
   <si>
     <t>{0}/{1}</t>
+  </si>
+  <si>
+    <t>普通攻击</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>逃跑</t>
+  </si>
+  <si>
+    <t>魔物</t>
+  </si>
+  <si>
+    <t>额外技能</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1241,9 @@
       <c r="A16">
         <v>910012</v>
       </c>
-      <c r="B16"/>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
       <c r="C16">
         <v>3</v>
       </c>
@@ -1235,7 +1252,9 @@
       <c r="A17">
         <v>910013</v>
       </c>
-      <c r="B17"/>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
       <c r="C17">
         <v>3</v>
       </c>
@@ -1244,7 +1263,9 @@
       <c r="A18">
         <v>910014</v>
       </c>
-      <c r="B18"/>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
       <c r="C18">
         <v>3</v>
       </c>
@@ -1253,7 +1274,9 @@
       <c r="A19">
         <v>910015</v>
       </c>
-      <c r="B19"/>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
       <c r="C19">
         <v>3</v>
       </c>
@@ -1262,19 +1285,27 @@
       <c r="A20">
         <v>910016</v>
       </c>
-      <c r="B20"/>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
       <c r="C20">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>910017</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>910018</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:1">

--- a/Config/Excel/language/lang_system.xlsx
+++ b/Config/Excel/language/lang_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -98,6 +98,21 @@
   </si>
   <si>
     <t>额外技能</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>帽子</t>
+  </si>
+  <si>
+    <t>盾牌</t>
+  </si>
+  <si>
+    <t>饰品</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1080,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="19.6333333333333" customWidth="1"/>
@@ -1292,55 +1307,102 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>910017</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>910018</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="C22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>910019</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>910020</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>910021</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>910022</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>910023</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>910024</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="C28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>910025</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/language/lang_system.xlsx
+++ b/Config/Excel/language/lang_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
     <t>xx</t>
   </si>
   <si>
-    <t>新游戏</t>
+    <t>开始游戏</t>
   </si>
   <si>
     <t>读取游戏</t>

--- a/Config/Excel/language/lang_system.xlsx
+++ b/Config/Excel/language/lang_system.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -98,6 +98,36 @@
   </si>
   <si>
     <t>额外技能</t>
+  </si>
+  <si>
+    <t>新获得</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>常规</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>帽子</t>
+  </si>
+  <si>
+    <t>衣服</t>
+  </si>
+  <si>
+    <t>裤子</t>
+  </si>
+  <si>
+    <t>鞋子</t>
+  </si>
+  <si>
+    <t>饰品</t>
+  </si>
+  <si>
+    <t>贵重物</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="19.6333333333333" customWidth="1"/>
@@ -1308,39 +1338,99 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>910019</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>910020</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>910021</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>910022</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>910023</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>910024</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>910025</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>910026</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>910027</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>910028</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>910029</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>910030</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>910031</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/language/lang_system.xlsx
+++ b/Config/Excel/language/lang_system.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20379"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\language\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project001\Config\Excel\language\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BF8693-6F77-48A3-A919-1257DE37A4AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABF9007-87A3-42C1-8B49-6C30B89F6F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -22,18 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
   <si>
     <t>text</t>
   </si>
   <si>
-    <t>color</t>
-  </si>
-  <si>
     <t>c</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
   <si>
     <t>string</t>
@@ -584,342 +578,282 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.625" customWidth="1"/>
-    <col min="2" max="2" width="37.25" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="37.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A19" s="1" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B22" t="s">
         <v>19</v>
       </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A21" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A22" s="1" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A24" s="1" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A25" s="1" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A26" s="1" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A27" s="1" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A28" s="1" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A29" s="1" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A30" s="1" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A31" s="1" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A32" s="1" t="s">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A33" s="1" t="s">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A34" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A35" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -932,7 +866,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -943,7 +877,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
